--- a/CANTEEN-REPORT-2025-2026-2 (1).xlsx
+++ b/CANTEEN-REPORT-2025-2026-2 (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronal\OneDrive\Desktop\New folder (11)\backend\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d83244719a67419/Desktop/New folder (11)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74D8BFD-E914-4CA7-BBD0-84A2922F45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{D74D8BFD-E914-4CA7-BBD0-84A2922F45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C71216C5-AC34-415B-A47A-E53E47715DDF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -831,53 +831,18 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -898,11 +863,46 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1347,7 +1347,7 @@
         <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
+    <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
@@ -1600,7 +1600,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -1610,7 +1610,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -1620,7 +1620,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -1630,7 +1630,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -1639,7 +1639,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -1651,7 +1651,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -1663,7 +1663,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -1675,7 +1675,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -1687,7 +1687,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -1699,7 +1699,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -1711,7 +1711,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -1720,7 +1720,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -1732,7 +1732,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="48"/>
@@ -1791,10 +1791,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="54">
-        <v>0</v>
-      </c>
-      <c r="G16" s="55"/>
+      <c r="F16" s="68">
+        <v>0</v>
+      </c>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -1804,10 +1804,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -1817,11 +1817,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -1851,10 +1851,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -1864,10 +1864,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -1877,10 +1877,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -1890,10 +1890,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -1903,10 +1903,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -1916,10 +1916,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -1929,10 +1929,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -1942,7 +1942,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -1965,8 +1965,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -1987,7 +1987,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -2000,7 +2000,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -2013,7 +2013,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -2028,7 +2028,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -2038,11 +2038,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -2270,23 +2270,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -2298,7 +2298,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -2311,7 +2311,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -2319,7 +2319,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -2346,18 +2346,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -4818,12 +4818,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -4836,31 +4855,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.7" top="0.31" bottom="0.31" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait"/>
@@ -4881,7 +4881,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -4891,7 +4891,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -4901,7 +4901,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -4911,7 +4911,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -4920,7 +4920,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -4932,7 +4932,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -4944,7 +4944,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -4956,7 +4956,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -4968,7 +4968,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -4980,7 +4980,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -4992,7 +4992,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -5001,7 +5001,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -5013,7 +5013,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="48"/>
@@ -5073,10 +5073,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -5086,10 +5086,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -5099,11 +5099,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -5133,10 +5133,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -5146,10 +5146,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -5159,10 +5159,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -5172,10 +5172,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -5185,10 +5185,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -5198,10 +5198,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -5211,10 +5211,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -5224,7 +5224,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -5247,8 +5247,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -5269,7 +5269,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -5282,7 +5282,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -5295,7 +5295,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -5310,7 +5310,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -5320,11 +5320,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -5558,23 +5558,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -5586,7 +5586,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -5599,7 +5599,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -5607,7 +5607,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -5634,18 +5634,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -8106,12 +8106,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -8124,31 +8143,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -8170,7 +8170,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -8180,7 +8180,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -8190,7 +8190,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -8200,7 +8200,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -8209,7 +8209,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -8221,7 +8221,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -8233,7 +8233,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -8245,7 +8245,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -8257,7 +8257,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -8269,7 +8269,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -8281,7 +8281,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -8290,7 +8290,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -8302,7 +8302,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="48"/>
@@ -8362,10 +8362,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -8375,10 +8375,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -8388,11 +8388,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -8422,10 +8422,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -8435,10 +8435,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -8448,10 +8448,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -8461,10 +8461,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -8474,10 +8474,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -8487,10 +8487,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -8500,10 +8500,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -8513,7 +8513,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -8536,8 +8536,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -8558,7 +8558,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -8571,7 +8571,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -8584,7 +8584,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -8599,7 +8599,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -8609,11 +8609,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -8839,7 +8839,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -8847,23 +8847,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -8875,7 +8875,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -8888,7 +8888,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -8896,7 +8896,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -8923,18 +8923,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -11395,12 +11395,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -11413,31 +11432,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11458,7 +11458,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -11468,7 +11468,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -11478,7 +11478,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -11488,7 +11488,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -11497,7 +11497,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -11509,7 +11509,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -11521,7 +11521,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -11533,7 +11533,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -11545,7 +11545,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -11557,7 +11557,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -11569,7 +11569,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -11578,7 +11578,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -11590,7 +11590,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="48"/>
@@ -11650,10 +11650,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -11663,10 +11663,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -11676,11 +11676,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -11710,10 +11710,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -11723,10 +11723,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -11736,10 +11736,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -11749,10 +11749,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -11762,10 +11762,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -11775,10 +11775,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -11788,10 +11788,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -11801,7 +11801,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -11824,8 +11824,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -11846,7 +11846,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -11859,7 +11859,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -11872,7 +11872,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -11887,7 +11887,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -11897,11 +11897,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -12127,7 +12127,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -12135,23 +12135,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -12163,7 +12163,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -12176,7 +12176,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -12184,7 +12184,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -12211,18 +12211,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -14683,12 +14683,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -14701,31 +14720,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="75" orientation="portrait"/>
@@ -14745,7 +14745,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -14754,7 +14754,7 @@
       <c r="G1" s="48"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -14763,7 +14763,7 @@
       <c r="G2" s="48"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -14772,7 +14772,7 @@
       <c r="G3" s="48"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -14781,7 +14781,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -14792,7 +14792,7 @@
       <c r="G5" s="48"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -14803,7 +14803,7 @@
       <c r="G6" s="48"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -14814,7 +14814,7 @@
       <c r="G7" s="48"/>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -14825,7 +14825,7 @@
       <c r="G8" s="48"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -14836,7 +14836,7 @@
       <c r="G9" s="48"/>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -14847,7 +14847,7 @@
       <c r="G10" s="48"/>
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -14856,7 +14856,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -14867,7 +14867,7 @@
       <c r="G12" s="48"/>
     </row>
     <row r="13" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="48"/>
@@ -14908,10 +14908,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -14921,10 +14921,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -14934,11 +14934,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1">
       <c r="A19" s="8"/>
@@ -14968,10 +14968,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -14981,10 +14981,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -14994,10 +14994,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -15007,10 +15007,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -15020,10 +15020,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -15033,10 +15033,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -15046,10 +15046,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -15059,7 +15059,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -15082,8 +15082,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -15104,7 +15104,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -15117,7 +15117,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -15130,7 +15130,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -15145,7 +15145,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -15155,11 +15155,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -15384,7 +15384,7 @@
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -15392,23 +15392,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -15420,7 +15420,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -15433,7 +15433,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -15441,7 +15441,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -15468,11 +15468,11 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="14.25" customHeight="1"/>
@@ -16416,6 +16416,36 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A61:B61"/>
@@ -16427,36 +16457,6 @@
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="E51:F51"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -16477,7 +16477,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -16487,7 +16487,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -16497,7 +16497,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -16507,7 +16507,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -16516,7 +16516,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -16528,7 +16528,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -16540,7 +16540,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -16552,7 +16552,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -16564,7 +16564,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -16576,7 +16576,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -16588,7 +16588,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -16597,7 +16597,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -16609,7 +16609,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="48"/>
@@ -16670,10 +16670,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -16683,10 +16683,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -16696,11 +16696,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -16730,10 +16730,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -16743,10 +16743,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -16756,10 +16756,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -16769,10 +16769,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -16782,10 +16782,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -16795,10 +16795,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -16808,10 +16808,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -16821,7 +16821,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -16844,8 +16844,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -16866,7 +16866,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -16879,7 +16879,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -16892,7 +16892,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -16907,7 +16907,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -16917,11 +16917,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -17147,7 +17147,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -17155,23 +17155,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -17183,7 +17183,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -17196,7 +17196,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -17204,7 +17204,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -17231,18 +17231,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -19703,12 +19703,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -19721,31 +19740,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -19768,7 +19768,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -19778,7 +19778,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -19788,7 +19788,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -19798,7 +19798,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -19807,7 +19807,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -19819,7 +19819,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -19831,7 +19831,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -19843,7 +19843,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -19855,7 +19855,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -19867,7 +19867,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -19879,7 +19879,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -19888,7 +19888,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -19900,7 +19900,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="48"/>
@@ -19960,10 +19960,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -19973,10 +19973,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -19986,11 +19986,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -20020,10 +20020,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -20033,10 +20033,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -20046,10 +20046,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -20059,10 +20059,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -20072,10 +20072,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -20085,10 +20085,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -20098,10 +20098,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -20111,7 +20111,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -20134,8 +20134,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -20156,7 +20156,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -20169,7 +20169,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -20182,7 +20182,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -20197,7 +20197,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -20207,11 +20207,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -20437,7 +20437,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -20445,23 +20445,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -20473,7 +20473,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -20486,7 +20486,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -20494,7 +20494,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -20521,18 +20521,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65" t="s">
+      <c r="D62" s="49" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="48"/>
@@ -22995,12 +22995,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -23013,31 +23032,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -23059,7 +23059,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -23069,7 +23069,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -23079,7 +23079,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -23089,7 +23089,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -23098,7 +23098,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -23110,7 +23110,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -23122,7 +23122,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -23134,7 +23134,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -23146,7 +23146,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -23158,7 +23158,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -23170,7 +23170,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -23179,7 +23179,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -23191,7 +23191,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.4">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="48"/>
@@ -23251,10 +23251,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.4">
       <c r="A17" s="8" t="s">
@@ -23264,10 +23264,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.4">
       <c r="A18" s="8" t="s">
@@ -23277,11 +23277,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -23311,10 +23311,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
@@ -23324,10 +23324,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
@@ -23337,10 +23337,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
@@ -23350,10 +23350,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
@@ -23363,10 +23363,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
@@ -23376,10 +23376,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
@@ -23389,10 +23389,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -23402,7 +23402,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -23425,8 +23425,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -23447,7 +23447,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -23460,7 +23460,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -23473,7 +23473,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -23488,7 +23488,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -23498,11 +23498,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -23728,7 +23728,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -23736,23 +23736,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -23764,7 +23764,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -23777,7 +23777,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -23785,7 +23785,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -23812,18 +23812,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -26284,12 +26284,31 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -26302,31 +26321,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -26349,7 +26349,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -26359,7 +26359,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -26369,7 +26369,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -26379,7 +26379,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -26388,7 +26388,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -26400,7 +26400,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -26412,7 +26412,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -26424,7 +26424,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -26436,7 +26436,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -26448,7 +26448,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -26460,7 +26460,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -26469,7 +26469,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -26481,7 +26481,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="48"/>
@@ -26541,10 +26541,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -26554,10 +26554,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -26567,11 +26567,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -26601,10 +26601,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -26614,10 +26614,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -26627,10 +26627,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -26640,10 +26640,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -26653,10 +26653,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -26666,10 +26666,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -26679,10 +26679,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -26692,7 +26692,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -26715,8 +26715,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -26737,7 +26737,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -26750,7 +26750,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -26763,7 +26763,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -26778,7 +26778,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -26788,11 +26788,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -27018,7 +27018,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -27026,23 +27026,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -27054,7 +27054,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -27067,7 +27067,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -27075,7 +27075,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -27102,18 +27102,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -29574,12 +29574,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -29592,31 +29611,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -29638,7 +29638,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -29648,7 +29648,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -29658,7 +29658,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -29668,7 +29668,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -29677,7 +29677,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -29689,7 +29689,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -29701,7 +29701,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -29713,7 +29713,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -29725,7 +29725,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -29737,7 +29737,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -29749,7 +29749,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -29758,7 +29758,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -29770,7 +29770,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="48"/>
@@ -29830,10 +29830,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -29843,10 +29843,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -29856,11 +29856,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -29890,10 +29890,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -29903,10 +29903,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -29916,10 +29916,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -29929,10 +29929,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -29942,10 +29942,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -29955,10 +29955,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -29968,10 +29968,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -29981,7 +29981,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -30004,8 +30004,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -30026,7 +30026,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -30039,7 +30039,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -30052,7 +30052,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -30067,7 +30067,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -30077,11 +30077,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -30307,7 +30307,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -30315,23 +30315,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -30343,7 +30343,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -30356,7 +30356,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -30364,7 +30364,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -30391,18 +30391,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -32863,12 +32863,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -32881,31 +32900,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -32926,7 +32926,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -32936,7 +32936,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -32946,7 +32946,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -32956,7 +32956,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -32965,7 +32965,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -32977,7 +32977,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -32989,7 +32989,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -33001,7 +33001,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -33013,7 +33013,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -33025,7 +33025,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -33037,7 +33037,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -33046,7 +33046,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -33058,7 +33058,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="48"/>
@@ -33118,10 +33118,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -33131,10 +33131,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -33144,11 +33144,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -33178,10 +33178,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -33191,10 +33191,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -33204,10 +33204,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -33217,10 +33217,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -33230,10 +33230,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -33243,10 +33243,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -33256,10 +33256,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -33269,7 +33269,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -33292,8 +33292,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -33314,7 +33314,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -33327,7 +33327,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -33340,7 +33340,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -33355,7 +33355,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -33365,11 +33365,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -33595,7 +33595,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -33603,23 +33603,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -33631,7 +33631,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -33644,7 +33644,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -33652,7 +33652,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -33679,18 +33679,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -36151,12 +36151,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -36169,31 +36188,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -36214,7 +36214,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="51"/>
+      <c r="A1" s="70"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -36224,7 +36224,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="52"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -36234,7 +36234,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -36244,7 +36244,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -36253,7 +36253,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -36265,7 +36265,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -36277,7 +36277,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -36289,7 +36289,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -36301,7 +36301,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -36313,7 +36313,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -36325,7 +36325,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -36334,7 +36334,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -36346,7 +36346,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="48"/>
@@ -36406,10 +36406,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -36419,10 +36419,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -36432,11 +36432,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -36466,10 +36466,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -36479,10 +36479,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -36492,10 +36492,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -36505,10 +36505,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -36518,10 +36518,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -36531,10 +36531,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -36544,10 +36544,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -36557,7 +36557,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -36580,8 +36580,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -36602,7 +36602,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -36615,7 +36615,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -36628,7 +36628,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -36643,7 +36643,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -36653,11 +36653,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -36883,7 +36883,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -36891,23 +36891,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -36919,7 +36919,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -36932,7 +36932,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -36940,7 +36940,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -36967,18 +36967,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -39439,12 +39439,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -39457,31 +39476,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/CANTEEN-REPORT-2025-2026-2 (1).xlsx
+++ b/CANTEEN-REPORT-2025-2026-2 (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d83244719a67419/Desktop/New folder (11)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{D74D8BFD-E914-4CA7-BBD0-84A2922F45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{032C7936-3E27-4FAF-B236-E030563F215E}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{D74D8BFD-E914-4CA7-BBD0-84A2922F45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A73BE2EA-497C-48E4-8269-A354831A8A38}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="June" sheetId="1" r:id="rId1"/>
@@ -831,53 +831,18 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -898,11 +863,46 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1604,7 +1604,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -1614,7 +1614,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -1624,7 +1624,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -1634,7 +1634,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -1643,7 +1643,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -1655,7 +1655,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -1667,7 +1667,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -1679,7 +1679,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -1691,7 +1691,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -1703,7 +1703,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -1715,7 +1715,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -1724,7 +1724,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -1736,7 +1736,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="48"/>
@@ -1795,10 +1795,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="54">
-        <v>0</v>
-      </c>
-      <c r="G16" s="55"/>
+      <c r="F16" s="68">
+        <v>0</v>
+      </c>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -1808,10 +1808,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -1821,11 +1821,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -1855,10 +1855,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -1868,10 +1868,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -1881,10 +1881,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -1894,10 +1894,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -1907,10 +1907,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -1920,10 +1920,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -1933,10 +1933,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -1946,7 +1946,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -1969,8 +1969,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -1991,7 +1991,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -2004,7 +2004,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -2017,7 +2017,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -2032,7 +2032,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -2042,11 +2042,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -2274,23 +2274,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -2302,7 +2302,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -2315,7 +2315,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -2323,7 +2323,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -2350,18 +2350,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -4822,12 +4822,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -4840,31 +4859,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.7" top="0.31" bottom="0.31" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait"/>
@@ -4885,7 +4885,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -4895,7 +4895,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -4905,7 +4905,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -4915,7 +4915,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -4924,7 +4924,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -4936,7 +4936,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -4948,7 +4948,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -4960,7 +4960,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -4972,7 +4972,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -4984,7 +4984,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -4996,7 +4996,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -5005,7 +5005,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -5017,7 +5017,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="48"/>
@@ -5077,10 +5077,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -5090,10 +5090,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -5103,11 +5103,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -5137,10 +5137,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -5150,10 +5150,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -5163,10 +5163,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -5176,10 +5176,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -5189,10 +5189,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -5202,10 +5202,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -5215,10 +5215,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -5228,7 +5228,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -5251,8 +5251,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -5273,7 +5273,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -5286,7 +5286,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -5299,7 +5299,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -5314,7 +5314,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -5324,11 +5324,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -5562,23 +5562,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -5590,7 +5590,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -5603,7 +5603,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -5611,7 +5611,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -5638,18 +5638,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -8110,12 +8110,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -8128,31 +8147,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -8174,7 +8174,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -8184,7 +8184,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -8194,7 +8194,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -8204,7 +8204,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -8213,7 +8213,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -8225,7 +8225,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -8237,7 +8237,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -8249,7 +8249,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -8261,7 +8261,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -8273,7 +8273,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -8285,7 +8285,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -8294,7 +8294,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -8306,7 +8306,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="48"/>
@@ -8366,10 +8366,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -8379,10 +8379,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -8392,11 +8392,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -8426,10 +8426,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -8439,10 +8439,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -8452,10 +8452,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -8465,10 +8465,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -8478,10 +8478,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -8491,10 +8491,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -8504,10 +8504,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -8517,7 +8517,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -8540,8 +8540,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -8562,7 +8562,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -8575,7 +8575,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -8588,7 +8588,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -8603,7 +8603,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -8613,11 +8613,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -8843,7 +8843,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -8851,23 +8851,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -8879,7 +8879,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -8892,7 +8892,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -8900,7 +8900,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -8927,18 +8927,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -11399,12 +11399,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -11417,31 +11436,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11462,7 +11462,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -11472,7 +11472,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -11482,7 +11482,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -11492,7 +11492,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -11501,7 +11501,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -11513,7 +11513,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -11525,7 +11525,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -11537,7 +11537,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -11549,7 +11549,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -11561,7 +11561,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -11573,7 +11573,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -11582,7 +11582,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -11594,7 +11594,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="48"/>
@@ -11654,10 +11654,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -11667,10 +11667,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -11680,11 +11680,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -11714,10 +11714,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -11727,10 +11727,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -11740,10 +11740,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -11753,10 +11753,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -11766,10 +11766,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -11779,10 +11779,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -11792,10 +11792,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -11805,7 +11805,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -11828,8 +11828,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -11850,7 +11850,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -11863,7 +11863,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -11876,7 +11876,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -11891,7 +11891,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -11901,11 +11901,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -12131,7 +12131,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -12139,23 +12139,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -12167,7 +12167,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -12180,7 +12180,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -12188,7 +12188,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -12215,18 +12215,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -14687,12 +14687,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -14705,31 +14724,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="75" orientation="portrait"/>
@@ -14750,7 +14750,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -14760,7 +14760,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -14770,7 +14770,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -14780,7 +14780,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -14789,7 +14789,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -14801,7 +14801,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -14813,7 +14813,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -14825,7 +14825,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -14837,7 +14837,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -14849,7 +14849,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -14861,7 +14861,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -14870,7 +14870,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -14882,7 +14882,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="48"/>
@@ -14941,10 +14941,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="54">
-        <v>0</v>
-      </c>
-      <c r="G16" s="55"/>
+      <c r="F16" s="68">
+        <v>0</v>
+      </c>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -14954,10 +14954,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -14967,11 +14967,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -15001,10 +15001,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -15014,10 +15014,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -15027,10 +15027,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -15040,10 +15040,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -15053,10 +15053,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -15066,10 +15066,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -15079,10 +15079,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -15092,7 +15092,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -15115,8 +15115,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -15137,7 +15137,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -15150,7 +15150,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -15163,7 +15163,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -15178,7 +15178,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -15188,11 +15188,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -15412,7 +15412,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -15420,23 +15420,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -15448,7 +15448,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -15461,7 +15461,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -15469,7 +15469,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -15496,18 +15496,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -17968,17 +17968,30 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
@@ -17987,30 +18000,17 @@
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.7" top="0.31" bottom="0.31" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait"/>
@@ -18031,7 +18031,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -18041,7 +18041,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -18051,7 +18051,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -18061,7 +18061,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -18070,7 +18070,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -18082,7 +18082,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -18094,7 +18094,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -18106,7 +18106,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -18118,7 +18118,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -18130,7 +18130,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -18142,7 +18142,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -18151,7 +18151,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -18163,7 +18163,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="48"/>
@@ -18224,10 +18224,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -18237,10 +18237,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -18250,11 +18250,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -18284,10 +18284,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -18297,10 +18297,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -18310,10 +18310,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -18323,10 +18323,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -18336,10 +18336,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -18349,10 +18349,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -18362,10 +18362,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -18375,7 +18375,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -18398,8 +18398,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -18420,7 +18420,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -18433,7 +18433,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -18446,7 +18446,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -18461,7 +18461,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -18471,11 +18471,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -18515,29 +18515,29 @@
       <c r="A39" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="17" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C39" s="17" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D39" s="17" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E39" s="17" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F39" s="17" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G39" s="17" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="B39" s="17">
+        <f>July!B45</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="17">
+        <f>July!C45</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="17">
+        <f>July!D45</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="17">
+        <f>July!E45</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="17">
+        <f>July!F45</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="17">
+        <f>July!G45</f>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27.75" customHeight="1">
@@ -18701,7 +18701,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -18709,23 +18709,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -18737,7 +18737,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -18750,7 +18750,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -18758,7 +18758,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -18785,18 +18785,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -21257,12 +21257,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -21275,31 +21294,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -21322,7 +21322,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -21332,7 +21332,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -21342,7 +21342,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -21352,7 +21352,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -21361,7 +21361,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -21373,7 +21373,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -21385,7 +21385,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -21397,7 +21397,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -21409,7 +21409,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -21421,7 +21421,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -21433,7 +21433,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -21442,7 +21442,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -21454,7 +21454,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="48"/>
@@ -21514,10 +21514,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -21527,10 +21527,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -21540,11 +21540,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -21574,10 +21574,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -21587,10 +21587,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -21600,10 +21600,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -21613,10 +21613,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -21626,10 +21626,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -21639,10 +21639,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -21652,10 +21652,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -21665,7 +21665,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -21688,8 +21688,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -21710,7 +21710,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -21723,7 +21723,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -21736,7 +21736,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -21751,7 +21751,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -21761,11 +21761,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -21991,7 +21991,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -21999,23 +21999,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -22027,7 +22027,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -22040,7 +22040,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -22048,7 +22048,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -22075,18 +22075,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65" t="s">
+      <c r="D62" s="49" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="48"/>
@@ -24549,12 +24549,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -24567,31 +24586,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -24613,7 +24613,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -24623,7 +24623,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -24633,7 +24633,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -24643,7 +24643,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -24652,7 +24652,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -24664,7 +24664,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -24676,7 +24676,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -24688,7 +24688,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -24700,7 +24700,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -24712,7 +24712,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -24724,7 +24724,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -24733,7 +24733,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -24745,7 +24745,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.4">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="48"/>
@@ -24805,10 +24805,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.4">
       <c r="A17" s="8" t="s">
@@ -24818,10 +24818,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.4">
       <c r="A18" s="8" t="s">
@@ -24831,11 +24831,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -24865,10 +24865,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
@@ -24878,10 +24878,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
@@ -24891,10 +24891,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
@@ -24904,10 +24904,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
@@ -24917,10 +24917,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
@@ -24930,10 +24930,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
@@ -24943,10 +24943,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -24956,7 +24956,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -24979,8 +24979,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -25001,7 +25001,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -25014,7 +25014,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -25027,7 +25027,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -25042,7 +25042,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -25052,11 +25052,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -25282,7 +25282,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -25290,23 +25290,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -25318,7 +25318,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -25331,7 +25331,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -25339,7 +25339,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -25366,18 +25366,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -27838,12 +27838,31 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -27856,31 +27875,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -27903,7 +27903,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -27913,7 +27913,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -27923,7 +27923,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -27933,7 +27933,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -27942,7 +27942,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -27954,7 +27954,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -27966,7 +27966,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -27978,7 +27978,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -27990,7 +27990,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -28002,7 +28002,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -28014,7 +28014,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -28023,7 +28023,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -28035,7 +28035,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="48"/>
@@ -28095,10 +28095,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -28108,10 +28108,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -28121,11 +28121,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -28155,10 +28155,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -28168,10 +28168,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -28181,10 +28181,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -28194,10 +28194,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -28207,10 +28207,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -28220,10 +28220,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -28233,10 +28233,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -28246,7 +28246,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -28269,8 +28269,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -28291,7 +28291,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -28304,7 +28304,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -28317,7 +28317,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -28332,7 +28332,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -28342,11 +28342,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -28572,7 +28572,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -28580,23 +28580,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -28608,7 +28608,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -28621,7 +28621,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -28629,7 +28629,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -28656,18 +28656,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -31128,12 +31128,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -31146,31 +31165,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -31192,7 +31192,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -31202,7 +31202,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -31212,7 +31212,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -31222,7 +31222,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -31231,7 +31231,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -31243,7 +31243,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -31255,7 +31255,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -31267,7 +31267,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -31279,7 +31279,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -31291,7 +31291,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -31303,7 +31303,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -31312,7 +31312,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -31324,7 +31324,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="48"/>
@@ -31384,10 +31384,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -31397,10 +31397,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -31410,11 +31410,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -31444,10 +31444,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -31457,10 +31457,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -31470,10 +31470,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -31483,10 +31483,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -31496,10 +31496,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -31509,10 +31509,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -31522,10 +31522,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -31535,7 +31535,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -31558,8 +31558,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -31580,7 +31580,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -31593,7 +31593,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -31606,7 +31606,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -31621,7 +31621,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -31631,11 +31631,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -31861,7 +31861,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -31869,23 +31869,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -31897,7 +31897,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -31910,7 +31910,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -31918,7 +31918,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -31945,18 +31945,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -34417,12 +34417,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -34435,31 +34454,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -34480,7 +34480,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -34490,7 +34490,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -34500,7 +34500,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -34510,7 +34510,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -34519,7 +34519,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -34531,7 +34531,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -34543,7 +34543,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -34555,7 +34555,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -34567,7 +34567,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -34579,7 +34579,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -34591,7 +34591,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -34600,7 +34600,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -34612,7 +34612,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="48"/>
@@ -34672,10 +34672,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -34685,10 +34685,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -34698,11 +34698,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -34732,10 +34732,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -34745,10 +34745,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -34758,10 +34758,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -34771,10 +34771,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -34784,10 +34784,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -34797,10 +34797,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -34810,10 +34810,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -34823,7 +34823,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -34846,8 +34846,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -34868,7 +34868,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -34881,7 +34881,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -34894,7 +34894,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -34909,7 +34909,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -34919,11 +34919,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -35149,7 +35149,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -35157,23 +35157,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -35185,7 +35185,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -35198,7 +35198,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -35206,7 +35206,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -35233,18 +35233,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -37705,12 +37705,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -37723,31 +37742,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -37768,7 +37768,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="51"/>
+      <c r="A1" s="70"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -37778,7 +37778,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="52"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -37788,7 +37788,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -37798,7 +37798,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -37807,7 +37807,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -37819,7 +37819,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -37831,7 +37831,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -37843,7 +37843,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -37855,7 +37855,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -37867,7 +37867,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -37879,7 +37879,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -37888,7 +37888,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -37900,7 +37900,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="48"/>
@@ -37960,10 +37960,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -37973,10 +37973,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -37986,11 +37986,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -38020,10 +38020,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -38033,10 +38033,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -38046,10 +38046,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -38059,10 +38059,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -38072,10 +38072,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -38085,10 +38085,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -38098,10 +38098,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -38111,7 +38111,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -38134,8 +38134,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -38156,7 +38156,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -38169,7 +38169,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -38182,7 +38182,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -38197,7 +38197,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -38207,11 +38207,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -38437,7 +38437,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -38445,23 +38445,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -38473,7 +38473,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -38486,7 +38486,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -38494,7 +38494,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -38521,18 +38521,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -40993,12 +40993,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -41011,31 +41030,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/CANTEEN-REPORT-2025-2026-2 (1).xlsx
+++ b/CANTEEN-REPORT-2025-2026-2 (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d83244719a67419/Desktop/New folder (11)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{D74D8BFD-E914-4CA7-BBD0-84A2922F45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A73BE2EA-497C-48E4-8269-A354831A8A38}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D74D8BFD-E914-4CA7-BBD0-84A2922F45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FBBDD4C-FA99-45CB-B7D8-97EDF905FA4D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="June" sheetId="1" r:id="rId1"/>
@@ -831,18 +831,53 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -863,46 +898,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1604,7 +1604,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -1614,7 +1614,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -1624,7 +1624,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -1634,7 +1634,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -1643,7 +1643,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -1655,7 +1655,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -1667,7 +1667,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -1679,7 +1679,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -1691,7 +1691,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -1703,7 +1703,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -1715,7 +1715,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -1724,7 +1724,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -1736,7 +1736,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="48"/>
@@ -1795,10 +1795,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="68">
-        <v>0</v>
-      </c>
-      <c r="G16" s="51"/>
+      <c r="F16" s="54">
+        <v>0</v>
+      </c>
+      <c r="G16" s="55"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -1808,10 +1808,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -1821,11 +1821,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -1855,10 +1855,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -1868,10 +1868,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -1881,10 +1881,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -1894,10 +1894,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -1907,10 +1907,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -1920,10 +1920,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -1933,10 +1933,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -1946,7 +1946,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -1969,8 +1969,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -1991,7 +1991,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -2004,7 +2004,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -2017,7 +2017,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -2032,7 +2032,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -2042,11 +2042,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -2274,23 +2274,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -2302,7 +2302,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -2315,7 +2315,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -2323,7 +2323,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -2350,18 +2350,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -4822,31 +4822,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -4859,12 +4840,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.7" top="0.31" bottom="0.31" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait"/>
@@ -4885,7 +4885,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -4895,7 +4895,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -4905,7 +4905,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -4915,7 +4915,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -4924,7 +4924,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -4936,7 +4936,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -4948,7 +4948,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -4960,7 +4960,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -4972,7 +4972,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -4984,7 +4984,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -4996,7 +4996,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -5005,7 +5005,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -5017,7 +5017,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="48"/>
@@ -5077,10 +5077,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -5090,10 +5090,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -5103,11 +5103,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -5137,10 +5137,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -5150,10 +5150,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -5163,10 +5163,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -5176,10 +5176,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -5189,10 +5189,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -5202,10 +5202,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -5215,10 +5215,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -5228,7 +5228,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -5251,8 +5251,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -5273,7 +5273,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -5286,7 +5286,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -5299,7 +5299,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -5314,7 +5314,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -5324,11 +5324,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -5562,23 +5562,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -5590,7 +5590,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -5603,7 +5603,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -5611,7 +5611,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -5638,18 +5638,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -8110,31 +8110,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -8147,12 +8128,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -8174,7 +8174,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -8184,7 +8184,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -8194,7 +8194,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -8204,7 +8204,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -8213,7 +8213,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -8225,7 +8225,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -8237,7 +8237,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -8249,7 +8249,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -8261,7 +8261,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -8273,7 +8273,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -8285,7 +8285,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -8294,7 +8294,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -8306,7 +8306,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="48"/>
@@ -8366,10 +8366,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -8379,10 +8379,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -8392,11 +8392,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -8426,10 +8426,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -8439,10 +8439,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -8452,10 +8452,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -8465,10 +8465,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -8478,10 +8478,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -8491,10 +8491,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -8504,10 +8504,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -8517,7 +8517,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -8540,8 +8540,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -8562,7 +8562,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -8575,7 +8575,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -8588,7 +8588,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -8603,7 +8603,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -8613,11 +8613,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -8843,7 +8843,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -8851,23 +8851,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -8879,7 +8879,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -8892,7 +8892,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -8900,7 +8900,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -8927,18 +8927,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -11399,31 +11399,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -11436,12 +11417,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11462,7 +11462,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -11472,7 +11472,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -11482,7 +11482,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -11492,7 +11492,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -11501,7 +11501,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -11513,7 +11513,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -11525,7 +11525,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -11537,7 +11537,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -11549,7 +11549,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -11561,7 +11561,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -11573,7 +11573,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -11582,7 +11582,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -11594,7 +11594,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="48"/>
@@ -11654,10 +11654,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -11667,10 +11667,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -11680,11 +11680,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -11714,10 +11714,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -11727,10 +11727,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -11740,10 +11740,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -11753,10 +11753,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -11766,10 +11766,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -11779,10 +11779,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -11792,10 +11792,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -11805,7 +11805,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -11828,8 +11828,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -11850,7 +11850,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -11863,7 +11863,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -11876,7 +11876,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -11891,7 +11891,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -11901,11 +11901,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -12131,7 +12131,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -12139,23 +12139,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -12167,7 +12167,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -12180,7 +12180,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -12188,7 +12188,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -12215,18 +12215,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -14687,31 +14687,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -14724,12 +14705,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="75" orientation="portrait"/>
@@ -14750,7 +14750,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -14760,7 +14760,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -14770,7 +14770,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -14780,7 +14780,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -14789,7 +14789,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -14801,7 +14801,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -14813,7 +14813,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -14825,7 +14825,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -14837,7 +14837,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -14849,7 +14849,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -14861,7 +14861,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -14870,7 +14870,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -14882,7 +14882,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="48"/>
@@ -14941,10 +14941,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="68">
-        <v>0</v>
-      </c>
-      <c r="G16" s="51"/>
+      <c r="F16" s="54">
+        <v>0</v>
+      </c>
+      <c r="G16" s="55"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -14954,10 +14954,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -14967,11 +14967,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -15001,10 +15001,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -15014,10 +15014,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -15027,10 +15027,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -15040,10 +15040,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -15053,10 +15053,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -15066,10 +15066,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -15079,10 +15079,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -15092,7 +15092,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -15115,8 +15115,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -15137,7 +15137,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -15150,7 +15150,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -15163,7 +15163,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -15178,7 +15178,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -15188,11 +15188,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -15412,7 +15412,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -15420,23 +15420,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -15448,7 +15448,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -15461,7 +15461,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -15469,7 +15469,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -15496,18 +15496,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -17968,30 +17968,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
@@ -18005,12 +17987,30 @@
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="E51:F51"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.7" top="0.31" bottom="0.31" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait"/>
@@ -18031,7 +18031,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -18041,7 +18041,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -18051,7 +18051,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -18061,7 +18061,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -18070,7 +18070,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -18082,7 +18082,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -18094,7 +18094,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -18106,7 +18106,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -18118,7 +18118,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -18130,7 +18130,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -18142,7 +18142,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -18151,7 +18151,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -18163,7 +18163,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="48"/>
@@ -18207,9 +18207,9 @@
         <v>8</v>
       </c>
       <c r="B15" s="8"/>
-      <c r="C15" s="9" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="C15" s="9">
+        <f>July!H45</f>
+        <v>0</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -18224,10 +18224,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -18237,10 +18237,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -18250,11 +18250,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -18284,10 +18284,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -18297,10 +18297,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -18310,10 +18310,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -18323,10 +18323,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -18336,10 +18336,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -18349,10 +18349,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -18362,10 +18362,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -18375,7 +18375,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -18398,8 +18398,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -18420,7 +18420,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -18433,7 +18433,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -18446,7 +18446,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -18461,7 +18461,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -18471,11 +18471,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -18701,7 +18701,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -18709,23 +18709,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -18737,7 +18737,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -18750,7 +18750,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -18758,7 +18758,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -18785,18 +18785,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -21257,31 +21257,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -21294,12 +21275,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -21322,7 +21322,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -21332,7 +21332,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -21342,7 +21342,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -21352,7 +21352,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -21361,7 +21361,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -21373,7 +21373,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -21385,7 +21385,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -21397,7 +21397,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -21409,7 +21409,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -21421,7 +21421,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -21433,7 +21433,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -21442,7 +21442,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -21454,7 +21454,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="48"/>
@@ -21514,10 +21514,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -21527,10 +21527,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -21540,11 +21540,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -21574,10 +21574,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -21587,10 +21587,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -21600,10 +21600,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -21613,10 +21613,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -21626,10 +21626,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -21639,10 +21639,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -21652,10 +21652,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -21665,7 +21665,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -21688,8 +21688,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -21710,7 +21710,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -21723,7 +21723,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -21736,7 +21736,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -21751,7 +21751,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -21761,11 +21761,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -21991,7 +21991,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -21999,23 +21999,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -22027,7 +22027,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -22040,7 +22040,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -22048,7 +22048,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -22075,18 +22075,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49" t="s">
+      <c r="D62" s="65" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="48"/>
@@ -24549,31 +24549,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -24586,12 +24567,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -24613,7 +24613,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -24623,7 +24623,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -24633,7 +24633,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -24643,7 +24643,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -24652,7 +24652,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -24664,7 +24664,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -24676,7 +24676,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -24688,7 +24688,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -24700,7 +24700,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -24712,7 +24712,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -24724,7 +24724,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -24733,7 +24733,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -24745,7 +24745,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.4">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="48"/>
@@ -24805,10 +24805,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.4">
       <c r="A17" s="8" t="s">
@@ -24818,10 +24818,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.4">
       <c r="A18" s="8" t="s">
@@ -24831,11 +24831,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -24865,10 +24865,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
@@ -24878,10 +24878,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
@@ -24891,10 +24891,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
@@ -24904,10 +24904,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
@@ -24917,10 +24917,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
@@ -24930,10 +24930,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
@@ -24943,10 +24943,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -24956,7 +24956,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -24979,8 +24979,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -25001,7 +25001,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -25014,7 +25014,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -25027,7 +25027,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -25042,7 +25042,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -25052,11 +25052,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -25282,7 +25282,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -25290,23 +25290,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -25318,7 +25318,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -25331,7 +25331,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -25339,7 +25339,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -25366,18 +25366,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -27838,31 +27838,12 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -27875,12 +27856,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -27903,7 +27903,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -27913,7 +27913,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -27923,7 +27923,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -27933,7 +27933,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -27942,7 +27942,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -27954,7 +27954,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -27966,7 +27966,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -27978,7 +27978,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -27990,7 +27990,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -28002,7 +28002,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -28014,7 +28014,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -28023,7 +28023,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -28035,7 +28035,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="48"/>
@@ -28095,10 +28095,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -28108,10 +28108,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -28121,11 +28121,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -28155,10 +28155,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -28168,10 +28168,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -28181,10 +28181,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -28194,10 +28194,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -28207,10 +28207,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -28220,10 +28220,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -28233,10 +28233,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -28246,7 +28246,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -28269,8 +28269,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -28291,7 +28291,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -28304,7 +28304,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -28317,7 +28317,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -28332,7 +28332,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -28342,11 +28342,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -28572,7 +28572,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -28580,23 +28580,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -28608,7 +28608,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -28621,7 +28621,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -28629,7 +28629,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -28656,18 +28656,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -31128,31 +31128,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -31165,12 +31146,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -31192,7 +31192,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -31202,7 +31202,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -31212,7 +31212,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -31222,7 +31222,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -31231,7 +31231,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -31243,7 +31243,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -31255,7 +31255,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -31267,7 +31267,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -31279,7 +31279,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -31291,7 +31291,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -31303,7 +31303,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -31312,7 +31312,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -31324,7 +31324,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="48"/>
@@ -31384,10 +31384,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -31397,10 +31397,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -31410,11 +31410,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -31444,10 +31444,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -31457,10 +31457,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -31470,10 +31470,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -31483,10 +31483,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -31496,10 +31496,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -31509,10 +31509,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -31522,10 +31522,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -31535,7 +31535,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -31558,8 +31558,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -31580,7 +31580,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -31593,7 +31593,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -31606,7 +31606,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -31621,7 +31621,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -31631,11 +31631,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -31861,7 +31861,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -31869,23 +31869,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -31897,7 +31897,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -31910,7 +31910,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -31918,7 +31918,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -31945,18 +31945,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -34417,31 +34417,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -34454,12 +34435,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -34480,7 +34480,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="72"/>
+      <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -34490,7 +34490,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
+      <c r="A2" s="47"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -34500,7 +34500,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -34510,7 +34510,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -34519,7 +34519,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -34531,7 +34531,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -34543,7 +34543,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -34555,7 +34555,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -34567,7 +34567,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -34579,7 +34579,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -34591,7 +34591,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -34600,7 +34600,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -34612,7 +34612,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="48"/>
@@ -34672,10 +34672,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -34685,10 +34685,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -34698,11 +34698,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -34732,10 +34732,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -34745,10 +34745,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -34758,10 +34758,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -34771,10 +34771,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -34784,10 +34784,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -34797,10 +34797,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -34810,10 +34810,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -34823,7 +34823,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -34846,8 +34846,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -34868,7 +34868,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -34881,7 +34881,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -34894,7 +34894,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -34909,7 +34909,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -34919,11 +34919,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -35149,7 +35149,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -35157,23 +35157,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -35185,7 +35185,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -35198,7 +35198,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -35206,7 +35206,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -35233,18 +35233,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -37705,31 +37705,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -37742,12 +37723,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -37768,7 +37768,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="70"/>
+      <c r="A1" s="51"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -37778,7 +37778,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="71"/>
+      <c r="A2" s="52"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -37788,7 +37788,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -37798,7 +37798,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="66"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -37807,7 +37807,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -37819,7 +37819,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -37831,7 +37831,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -37843,7 +37843,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="52" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -37855,7 +37855,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -37867,7 +37867,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -37879,7 +37879,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -37888,7 +37888,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -37900,7 +37900,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="53" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="48"/>
@@ -37960,10 +37960,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="69">
-        <v>0</v>
-      </c>
-      <c r="G16" s="60"/>
+      <c r="F16" s="56">
+        <v>0</v>
+      </c>
+      <c r="G16" s="57"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -37973,10 +37973,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="69">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60"/>
+      <c r="F17" s="56">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -37986,11 +37986,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="63">
+      <c r="F18" s="58">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -38020,10 +38020,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51"/>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -38033,10 +38033,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="59">
-        <v>0</v>
-      </c>
-      <c r="G22" s="60"/>
+      <c r="F22" s="60">
+        <v>0</v>
+      </c>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -38046,10 +38046,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="65">
-        <v>0</v>
-      </c>
-      <c r="G23" s="60"/>
+      <c r="F23" s="61">
+        <v>0</v>
+      </c>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -38059,10 +38059,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60"/>
+      <c r="F24" s="60">
+        <v>0</v>
+      </c>
+      <c r="G24" s="57"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -38072,10 +38072,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="59">
-        <v>0</v>
-      </c>
-      <c r="G25" s="60"/>
+      <c r="F25" s="60">
+        <v>0</v>
+      </c>
+      <c r="G25" s="57"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -38085,10 +38085,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="59">
-        <v>0</v>
-      </c>
-      <c r="G26" s="60"/>
+      <c r="F26" s="60">
+        <v>0</v>
+      </c>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -38098,10 +38098,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="59">
-        <v>0</v>
-      </c>
-      <c r="G27" s="60"/>
+      <c r="F27" s="60">
+        <v>0</v>
+      </c>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -38111,7 +38111,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="61">
+      <c r="F28" s="62">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -38134,8 +38134,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="51"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -38156,7 +38156,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -38169,7 +38169,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="52"/>
+      <c r="D33" s="64"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -38182,7 +38182,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="52"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -38197,7 +38197,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="55">
+      <c r="F35" s="68">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -38207,11 +38207,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="57">
+      <c r="F36" s="70">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -38437,7 +38437,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="58"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -38445,23 +38445,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="47" t="s">
+      <c r="A50" s="72" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="72" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="67" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -38473,7 +38473,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -38486,7 +38486,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -38494,7 +38494,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -38521,18 +38521,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="51"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="51"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="55"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="49"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -40993,31 +40993,12 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -41030,12 +41011,31 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
